--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Automation_eFMS_Vendor\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9E9033-5A5B-42C3-AD02-89E3F4383AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30128"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C579ECF-95BA-48AC-83F1-AE309011AED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Vendor_Payment" sheetId="1" r:id="rId1"/>
+    <sheet name="VENDOR_PAYMENT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,64 +36,64 @@
     <t>MST</t>
   </si>
   <si>
-    <t>Vendor Code</t>
-  </si>
-  <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Số Hợp Đồng</t>
-  </si>
-  <si>
-    <t>Hạn Hợp Đồng</t>
-  </si>
-  <si>
-    <t>Hạn Thanh toán</t>
-  </si>
-  <si>
-    <t>Dịch vụ</t>
+    <t>VENDOR CODE</t>
+  </si>
+  <si>
+    <t>VENDOR NAME</t>
+  </si>
+  <si>
+    <t>SỐ HỢP ĐỒNG</t>
+  </si>
+  <si>
+    <t>HẠN HỢP ĐỒNG</t>
+  </si>
+  <si>
+    <t>HẠN THANH TOÁN</t>
+  </si>
+  <si>
+    <t>DỊCH VỤ</t>
   </si>
   <si>
     <t>NCC</t>
   </si>
   <si>
-    <t>Số ĐNTT-FMS</t>
-  </si>
-  <si>
-    <t>Số Hóa Đơn/Bang kê</t>
-  </si>
-  <si>
-    <t>Ngày Hóa Đơn</t>
-  </si>
-  <si>
-    <t>Số tiền</t>
-  </si>
-  <si>
-    <t>Ngày Lập-FMS</t>
-  </si>
-  <si>
-    <t>Ngày duyệt-HOD</t>
-  </si>
-  <si>
-    <t>Ngày kế toán đã kiểm tra</t>
-  </si>
-  <si>
-    <t>Ghi chú (nếu bị thiếu chứng)</t>
-  </si>
-  <si>
-    <t>Ngày CK dự kiến</t>
-  </si>
-  <si>
-    <t>Over due date</t>
-  </si>
-  <si>
-    <t>Lý do chưa thanh toán</t>
-  </si>
-  <si>
-    <t>Số Báo Nợ</t>
-  </si>
-  <si>
-    <t>Tình Trạng</t>
+    <t>SỐ ĐNTT-FMS</t>
+  </si>
+  <si>
+    <t>SỐ HOÁ ĐƠN/BANG KÊ</t>
+  </si>
+  <si>
+    <t>NGÀY HOÁ ĐƠN</t>
+  </si>
+  <si>
+    <t>SỐ TIỀN</t>
+  </si>
+  <si>
+    <t>NGÀY LẬP - FMS</t>
+  </si>
+  <si>
+    <t>NGÀY DUYỆT - HOD</t>
+  </si>
+  <si>
+    <t>NGÀY KẾ TOÁN ĐÃ KIỂM TRA</t>
+  </si>
+  <si>
+    <t>GHI CHÚ (NẾU BỊ THIẾU CHỨNG)</t>
+  </si>
+  <si>
+    <t>NGÀY CK DỰ KIẾN</t>
+  </si>
+  <si>
+    <t>OVER DUE DATE</t>
+  </si>
+  <si>
+    <t>LÝ DO CHƯA THANH TOÁN</t>
+  </si>
+  <si>
+    <t>SỐ BÁO NỢ</t>
+  </si>
+  <si>
+    <t>TÌNH TRẠNG</t>
   </si>
   <si>
     <t>CHI HỘ</t>
@@ -92,31 +103,29 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="12"/>
       <color rgb="FFFFFF00"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -129,13 +138,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF275317"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,18 +160,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -193,39 +199,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -277,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -388,6 +394,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -396,13 +409,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -467,31 +473,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -499,34 +485,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="36.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="11.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.77734375" style="4" customWidth="1"/>
-    <col min="16" max="16" width="24.33203125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="28.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="32.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="26.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15.7109375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -593,7 +580,6 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C579ECF-95BA-48AC-83F1-AE309011AED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366BF723-4551-4D2E-88B4-FFB3E04DF25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDOR_PAYMENT" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,7 +113,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,14 +121,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,8 +147,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -156,20 +162,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -189,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -335,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -477,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -486,102 +513,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="28.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="32.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="18.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="26.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="15.7109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="49.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.88671875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="26.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15.6640625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:22" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366BF723-4551-4D2E-88B4-FFB3E04DF25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95348B2A-ABBE-4E45-99EE-51FD0B81B1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDOR_PAYMENT" sheetId="1" r:id="rId1"/>

--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95348B2A-ABBE-4E45-99EE-51FD0B81B1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8E710D-49BC-4163-821D-7D8A8CE3156C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDOR_PAYMENT" sheetId="1" r:id="rId1"/>
@@ -515,8 +515,8 @@
   <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5546875" style="2" customWidth="1"/>

--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8E710D-49BC-4163-821D-7D8A8CE3156C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BA5777-A033-4D6F-B604-4A9A1E497330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>MST</t>
   </si>
@@ -57,46 +57,49 @@
     <t>NCC</t>
   </si>
   <si>
+    <t>SỐ HOÁ ĐƠN/BANG KÊ</t>
+  </si>
+  <si>
+    <t>NGÀY HOÁ ĐƠN</t>
+  </si>
+  <si>
+    <t>NGÀY LẬP - FMS</t>
+  </si>
+  <si>
+    <t>NGÀY DUYỆT - HOD</t>
+  </si>
+  <si>
+    <t>NGÀY KẾ TOÁN ĐÃ KIỂM TRA</t>
+  </si>
+  <si>
+    <t>GHI CHÚ (NẾU BỊ THIẾU CHỨNG)</t>
+  </si>
+  <si>
+    <t>NGÀY CK DỰ KIẾN</t>
+  </si>
+  <si>
+    <t>OVER DUE DATE</t>
+  </si>
+  <si>
+    <t>LÝ DO CHƯA THANH TOÁN</t>
+  </si>
+  <si>
+    <t>SỐ BÁO NỢ</t>
+  </si>
+  <si>
+    <t>TÌNH TRẠNG</t>
+  </si>
+  <si>
+    <t>CHI HỘ</t>
+  </si>
+  <si>
+    <t>GROUP EFMS</t>
+  </si>
+  <si>
     <t>SỐ ĐNTT-FMS</t>
   </si>
   <si>
-    <t>SỐ HOÁ ĐƠN/BANG KÊ</t>
-  </si>
-  <si>
-    <t>NGÀY HOÁ ĐƠN</t>
-  </si>
-  <si>
-    <t>SỐ TIỀN</t>
-  </si>
-  <si>
-    <t>NGÀY LẬP - FMS</t>
-  </si>
-  <si>
-    <t>NGÀY DUYỆT - HOD</t>
-  </si>
-  <si>
-    <t>NGÀY KẾ TOÁN ĐÃ KIỂM TRA</t>
-  </si>
-  <si>
-    <t>GHI CHÚ (NẾU BỊ THIẾU CHỨNG)</t>
-  </si>
-  <si>
-    <t>NGÀY CK DỰ KIẾN</t>
-  </si>
-  <si>
-    <t>OVER DUE DATE</t>
-  </si>
-  <si>
-    <t>LÝ DO CHƯA THANH TOÁN</t>
-  </si>
-  <si>
-    <t>SỐ BÁO NỢ</t>
-  </si>
-  <si>
-    <t>TÌNH TRẠNG</t>
-  </si>
-  <si>
-    <t>CHI HỘ</t>
+    <t>SỐ TIỀN99</t>
   </si>
 </sst>
 </file>
@@ -512,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
@@ -522,25 +525,26 @@
     <col min="5" max="5" width="20.5546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.88671875" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="49.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.33203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="18.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="20" style="1" customWidth="1"/>
     <col min="15" max="15" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="18.88671875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="26.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="15.6640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="16.88671875" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.109375" style="1"/>
+    <col min="16" max="16" width="14.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="18.88671875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="19.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="26.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5546875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="16.88671875" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -566,46 +570,49 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/Vendor_Payment_Template.xlsx
+++ b/data/Vendor_Payment_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BA5777-A033-4D6F-B604-4A9A1E497330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A128C7F-5997-4E62-A792-920332141BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>SỐ ĐNTT-FMS</t>
   </si>
   <si>
-    <t>SỐ TIỀN99</t>
+    <t>SỐ TIỀN</t>
   </si>
 </sst>
 </file>
@@ -525,7 +525,7 @@
     <col min="5" max="5" width="20.5546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.88671875" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.109375" style="1" customWidth="1"/>
